--- a/Artefato 3.xlsx
+++ b/Artefato 3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/ferrarini_isabela_pucpr_edu_br/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\ChecklistQualidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D8E0D60-FFC3-41E3-A8E7-8BAED5E0A4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31059D23-A460-4F70-A289-8F58648E6605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AD0D3937-53B7-4C00-80DB-5BBA5D567A81}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>n°</t>
   </si>
@@ -156,13 +156,28 @@
   </si>
   <si>
     <t>Mariana</t>
+  </si>
+  <si>
+    <t>Aderência Por Área</t>
+  </si>
+  <si>
+    <t>Total de Perguntas</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Não Aplicavél</t>
+  </si>
+  <si>
+    <t>Aderência</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +210,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -205,7 +235,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFA6124E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -237,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -248,12 +278,48 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFA6124E"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -271,10 +337,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6F584FC-A5BE-427A-BF40-6EFDB06653A1}" name="Table1" displayName="Table1" ref="B1:I21" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6F584FC-A5BE-427A-BF40-6EFDB06653A1}" name="Table1" displayName="Table1" ref="B1:I21" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="B1:I21" xr:uid="{E6F584FC-A5BE-427A-BF40-6EFDB06653A1}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C491E1FB-C798-4CB3-80A6-3DFD3312A60E}" name="n°" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C491E1FB-C798-4CB3-80A6-3DFD3312A60E}" name="n°" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{C3282D55-C28C-4600-82C6-FF827ED58CB0}" name="Descrição"/>
     <tableColumn id="3" xr3:uid="{993FF359-2EA1-48F1-8170-F50845F66692}" name="Resultado "/>
     <tableColumn id="4" xr3:uid="{8F145B2F-9B32-4493-893A-D425BEA70BEB}" name="Responsavel"/>
@@ -283,12 +349,12 @@
     <tableColumn id="7" xr3:uid="{CCA3F520-3966-4EAC-893A-23C80109162A}" name="Ação Não Corretiva"/>
     <tableColumn id="8" xr3:uid="{06D75D27-0D2B-42AE-8549-A350C03E89D4}" name="Situação da NC "/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -617,28 +683,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -762,7 +828,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
         <v>16</v>
       </c>
@@ -770,7 +836,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
         <v>17</v>
       </c>
@@ -778,7 +844,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
         <v>18</v>
       </c>
@@ -786,7 +852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
         <v>19</v>
       </c>
@@ -794,7 +860,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
         <v>20</v>
       </c>
@@ -802,41 +868,75 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C23" s="6" t="s">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D23" s="11"/>
+      <c r="F23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C24" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C25" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F25" s="9"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="10"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C26" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F26" s="5">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C28" s="5" t="s">
         <v>35</v>
       </c>
@@ -844,19 +944,26 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C29" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D29" s="5"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C30" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D30" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I24:I25"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -874,15 +981,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
     <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
@@ -1032,6 +1130,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1DD7AEA-0F16-4812-9CB4-B4A9D955A9E2}">
   <ds:schemaRefs>
@@ -1049,14 +1156,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C39528C1-3F3D-4F42-8119-936F8AFAB22A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9516A9F-BD2F-4061-A991-438BE9F7F39C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1074,6 +1173,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C39528C1-3F3D-4F42-8119-936F8AFAB22A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8a1ef6c3-8324-4103-bf4a-1328c5dc3653}" enabled="0" method="" siteId="{8a1ef6c3-8324-4103-bf4a-1328c5dc3653}" removed="1"/>
